--- a/ไฟล์ใช้ Import ทดสอบระบบ/Import Course/1.1 ใช้ 1 ห้อง นักเรียนลงเรียนครบทุกคน/อาจารคนที่3/คอร์สที่1 อังคาร AM.xlsx
+++ b/ไฟล์ใช้ Import ทดสอบระบบ/Import Course/1.1 ใช้ 1 ห้อง นักเรียนลงเรียนครบทุกคน/อาจารคนที่3/คอร์สที่1 อังคาร AM.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563A9684-4280-4CCB-B526-0C4D967753E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E457E23-3C73-4DAE-BBA2-760553F105BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="405" windowWidth="26760" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ISRP37" sheetId="1" r:id="rId1"/>
@@ -242,9 +242,6 @@
     <t>วันเวลาที่พิมพ์ : 27/02/2566 - 11:48:10 น. ผู้พิมพ์ : อาจารย์ วรณัน  วรมงคล IP Address : 115.87.199.61</t>
   </si>
   <si>
-    <t>ภาคการศึกษาที่ : 2    ปีการศึกษา : 2566</t>
-  </si>
-  <si>
     <t>ชื่อวิชา : CPE5005 วิศวะกรรมซอฟ์แวร์และระบบ	 :  3(2-2-5)</t>
   </si>
   <si>
@@ -252,13 +249,16 @@
   </si>
   <si>
     <t>วันเวลาเรียน : อังคาร 09:00-11:00    ห้องเรียน : 42/4222</t>
+  </si>
+  <si>
+    <t>ภาคการศึกษาที่ : 2    ปีการศึกษา : 2568</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,14 +367,14 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -394,9 +394,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีม Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -434,7 +434,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -540,7 +540,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -682,7 +682,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F40"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -704,95 +704,95 @@
     <col min="6" max="6" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>1</v>
       </c>
@@ -832,7 +832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2</v>
       </c>
@@ -852,7 +852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>3</v>
       </c>
@@ -872,7 +872,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>4</v>
       </c>
@@ -890,7 +890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>5</v>
       </c>
@@ -908,7 +908,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>6</v>
       </c>
@@ -928,7 +928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>7</v>
       </c>
@@ -948,7 +948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="18" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>8</v>
       </c>
@@ -966,7 +966,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>9</v>
       </c>
@@ -986,7 +986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>10</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>11</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>12</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>13</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>14</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>15</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>16</v>
       </c>
@@ -1118,7 +1118,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="27" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>17</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="28" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>18</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="29" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>19</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="30" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>20</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="31" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>21</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="32" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>22</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="33" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>23</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="34" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>24</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="35" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>25</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="36" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>26</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="37" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>27</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="38" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>28</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="20.100000000000001" customHeight="1">
+    <row r="39" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>29</v>
       </c>
@@ -1362,28 +1362,28 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A40" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
